--- a/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule. Maman dit : coq, poule, poussin. Ce sont trois noms. Près du foin, un cheval mange. Une jument est là. Un poulain reste près. Maman dit : cheval, jument, poulain. Un chien court. Une chienne le suit. Un chiot dort. Maman dit : chien, chienne, chiot. Hugo répète les trois noms de la famille.</t>
+          <t>Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule. Coq, poule, poussin. Ce sont trois noms. Près du foin, un cheval mange. Une jument est là. Un poulain reste près. Cheval, jument, poulain. Un chien court. Une chienne le suit. Un chiot dort. Chien, chienne, chiot. Hugo répète les trois noms de la famille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule.
+maman|Coq, poule, poussin. Ce sont trois noms. Près du foin, un cheval mange.
+narrateur|Une jument est là. Un poulain reste près.
+maman|Cheval, jument, poulain.
+narrateur|Un chien court. Une chienne le suit. Un chiot dort.
+maman|Chien, chienne, chiot.
+narrateur|Hugo répète les trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo caresse le foin. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Hugo répète les trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Hugo a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Hugo caresse le foin. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trois noms à la ferme</t>
+          <t>La chèvre derrière la paille</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut parler à la chèvre. Elle voit une poule, puis une vache. La chèvre est derrière le tas de paille, avec le chevreau. Sarah l'appelle, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule. Coq, poule, poussin. Ce sont trois noms. Près du foin, un cheval mange. Une jument est là. Un poulain reste près. Cheval, jument, poulain. Un chien court. Une chienne le suit. Un chiot dort. Chien, chienne, chiot. Hugo répète les trois noms de la famille.</t>
+          <t>Sur le toit de la grange, la rosée brille. Elle fait des perles toutes petites. La cour sent le foin tiède. Un seau de zinc brille près du puits. Sarah vit ici, avec maman. Les bottes attendent près de la porte. Elles sont encore un peu humides. Maman, je veux voir la chèvre. La chèvre du fond ? Oui. Je veux lui parler. En ce moment, Sarah prend sa veste. La veste sent encore le foin. On va la chercher ensemble ? Oui, maman. Maman ouvre la porte de la cour. L'air sent la paille chaude. Un peu de poussière dore le soleil. Sarah marche près de maman. Une poule rouge picore près du portail. Une poule ! Oui. Elle picore le grain. Sarah s'arrête un peu. Elle regarde la poule, tout doux. Puis elle reprend le chemin. Plus loin, une vache lèche une pierre. Une vache ! Oui, Sarah. Elle lèche le sel. Sarah pose la main sur la clôture. Le bois est chaud, un peu rêche. La chèvre est où ? On va au pré ? Le pré est vide, tout calme. L'herbe est rase, encore mouillée. Elle n'est pas là. On écoute ? Sarah tend l'oreille. Un bêlement vient de derrière. J'entends ! Derrière le tas de paille ? Oui ! Le tas de paille est haut. Il sent le blé chaud. Sarah tourne autour, tout doucement. Des brins collent à sa veste. Derrière le tas, deux oreilles bougent. La chèvre ! La chèvre lèche un petit chevreau. Tu vois le petit ? Le chevreau. Oui. Bouc, chèvre, chevreau. Trois noms de la famille. Sarah s'accroupit près de maman. Bonjour, chèvre. La chèvre avance un peu. Son poil est rêche, tout chaud. Je te parlais. Elle t'écoute, Sarah. Tu lui parles tout doux. Sarah pose sa voix tout bas. Tu étais derrière la paille. Merci d'avoir écouté, Sarah. Tu as trouvé la chèvre. Avec le chevreau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule. Maman dit : coq, poule, poussin. Ce sont &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Près du foin, un cheval mange. Une jument est là. Un poulain reste près. Maman dit : cheval, jument, poulain. Un chien court. Une chienne le suit. Un chiot dort. Maman dit : chien, chienne, chiot. Hugo répète les trois noms de la famille.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le toit de la grange, la rosée brille. Elle fait des perles toutes petites. La cour sent le foin tiède. Un seau de zinc brille près du puits. Sarah vit ici, avec maman. Les bottes attendent près de la porte. Elles sont encore un peu humides. Maman, je veux voir la chèvre. La chèvre du fond ? Oui. Je veux lui parler. En ce moment, Sarah prend sa veste. La veste sent encore le foin. On va la chercher ensemble ? Oui, maman. Maman ouvre la porte de la cour. L'air sent la paille chaude. Un peu de poussière dore le soleil. Sarah marche près de maman. Une poule rouge picore près du portail. Une poule ! Oui. Elle picore le grain. Sarah s'arrête un peu. Elle regarde la poule, tout doux. Puis elle reprend le chemin. Plus loin, une vache lèche une pierre. Une vache ! Oui, Sarah. Elle lèche le sel. Sarah pose la main sur la clôture. Le bois est chaud, un peu rêche. La chèvre est où ? On va au pré ? Le pré est vide, tout calme. L'herbe est rase, encore mouillée. Elle n'est pas là. On écoute ? Sarah tend l'oreille. Un bêlement vient de derrière. J'entends ! Derrière le tas de paille ? Oui ! Le tas de paille est haut. Il sent le blé chaud. Sarah tourne autour, tout doucement. Des brins collent à sa veste. Derrière le tas, deux oreilles bougent. La chèvre ! La chèvre lèche un petit chevreau. Tu vois le petit ? Le chevreau. Oui. Bouc, chèvre, chevreau. Trois noms de la famille. Sarah s'accroupit près de maman. Bonjour, chèvre. La chèvre avance un peu. Son poil est rêche, tout chaud. Je te parlais. Elle t'écoute, Sarah. Tu lui parles tout doux. Sarah pose sa voix tout bas. Tu étais derrière la paille. Merci d'avoir écouté, Sarah. Tu as trouvé la chèvre. Avec le chevreau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est à la ferme avec maman. Dans la cour, un coq chante. Une poule picore. Un poussin suit la poule.
-maman|Coq, poule, poussin. Ce sont trois noms. Près du foin, un cheval mange.
-narrateur|Une jument est là. Un poulain reste près.
-maman|Cheval, jument, poulain.
-narrateur|Un chien court. Une chienne le suit. Un chiot dort.
-maman|Chien, chienne, chiot.
-narrateur|Hugo répète les trois noms de la famille.</t>
+          <t>narrateur|Sur le toit de la grange, la rosée brille.
+narrateur|Elle fait des perles toutes petites.
+narrateur|La cour sent le foin tiède.
+narrateur|Un seau de zinc brille près du puits.
+narrateur|Sarah vit ici, avec maman.
+narrateur|Les bottes attendent près de la porte.
+narrateur|Elles sont encore un peu humides.
+enfant-f|Maman, je veux voir la chèvre.
+maman|La chèvre du fond ?
+enfant-f|Oui.
+enfant-f|Je veux lui parler.
+narrateur|En ce moment, Sarah prend sa veste.
+narrateur|La veste sent encore le foin.
+maman|On va la chercher ensemble ?
+enfant-f|Oui, maman.
+narrateur|Maman ouvre la porte de la cour.
+narrateur|L'air sent la paille chaude.
+narrateur|Un peu de poussière dore le soleil.
+narrateur|Sarah marche près de maman.
+narrateur|Une poule rouge picore près du portail.
+enfant-f|Une poule !
+maman|Oui.
+maman|Elle picore le grain.
+narrateur|Sarah s'arrête un peu.
+narrateur|Elle regarde la poule, tout doux.
+narrateur|Puis elle reprend le chemin.
+narrateur|Plus loin, une vache lèche une pierre.
+enfant-f|Une vache !
+maman|Oui, Sarah.
+maman|Elle lèche le sel.
+narrateur|Sarah pose la main sur la clôture.
+narrateur|Le bois est chaud, un peu rêche.
+enfant-f|La chèvre est où ?
+maman|On va au pré ?
+narrateur|Le pré est vide, tout calme.
+narrateur|L'herbe est rase, encore mouillée.
+enfant-f|Elle n'est pas là.
+maman|On écoute ?
+narrateur|Sarah tend l'oreille.
+narrateur|Un bêlement vient de derrière.
+enfant-f|J'entends !
+maman|Derrière le tas de paille ?
+enfant-f|Oui !
+narrateur|Le tas de paille est haut.
+narrateur|Il sent le blé chaud.
+narrateur|Sarah tourne autour, tout doucement.
+narrateur|Des brins collent à sa veste.
+narrateur|Derrière le tas, deux oreilles bougent.
+enfant-f|La chèvre !
+narrateur|La chèvre lèche un petit chevreau.
+maman|Tu vois le petit ?
+enfant-f|Le chevreau.
+maman|Oui.
+maman|Bouc, chèvre, chevreau.
+maman|Trois noms de la famille.
+narrateur|Sarah s'accroupit près de maman.
+enfant-f|Bonjour, chèvre.
+narrateur|La chèvre avance un peu.
+narrateur|Son poil est rêche, tout chaud.
+enfant-f|Je te parlais.
+maman|Elle t'écoute, Sarah.
+maman|Tu lui parles tout doux.
+narrateur|Sarah pose sa voix tout bas.
+enfant-f|Tu étais derrière la paille.
+maman|Merci d'avoir écouté, Sarah.
+maman|Tu as trouvé la chèvre.
+enfant-f|Avec le chevreau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,12 +1422,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
+          <t>Derrière le tas de paille, qui est là ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Derrière le tas de paille, qui est là ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,12 +1437,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>chèvre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | petit | le petit</t>
+          <t>chèvre | le chèvre | un chèvre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1385,7 +1457,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le petit du coq et de la poule. Qui est-ce ?</t>
+          <t>C'est la chèvre. Qui est derrière la paille ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1434,7 +1506,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1578,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Derrière le tas de paille, qui est là ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
+          <t>La chèvre reste derrière la paille. Le chevreau tète encore. Il est tout petit. Oui. C'est le petit de la chèvre. Sarah tend un brin de foin. La chèvre le prend, tout calme. Tu lui parles encore ? Oui. Elle m'écoute. Un brin d'or colle à sa manche. On reste un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Coq, poule, poussin. Cheval, jument, poulain.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La chèvre reste derrière la paille. Le chevreau tète encore. Il est tout petit. Oui. C'est le petit de la chèvre. Sarah tend un brin de foin. La chèvre le prend, tout calme. Tu lui parles encore ? Oui. Elle m'écoute. Un brin d'or colle à sa manche. On reste un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,14 +1666,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1749,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|La chèvre reste derrière la paille.
+narrateur|Le chevreau tète encore.
+enfant-f|Il est tout petit.
+maman|Oui.
+maman|C'est le petit de la chèvre.
+narrateur|Sarah tend un brin de foin.
+narrateur|La chèvre le prend, tout calme.
+maman|Tu lui parles encore ?
+enfant-f|Oui.
+enfant-f|Elle m'écoute.
+narrateur|Un brin d'or colle à sa manche.
+maman|On reste un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1788,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo caresse le foin. Maman sourit.</t>
+          <t>Ils redescendent vers la cour. La poule picore encore. La vache lèche encore la pierre. Je les ai vues. La poule, la vache, la chèvre. Et le chevreau. Tu lui as parlé ? Oui. Sarah se retourne une fois. Le tas de paille cache encore les oreilles.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo caresse le foin. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils redescendent vers la cour. La poule picore encore. La vache lèche encore la pierre. Je les ai vues. La poule, la vache, la chèvre. Et le chevreau. Tu lui as parlé ? Oui. Sarah se retourne une fois. Le tas de paille cache encore les oreilles.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1849,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1924,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo caresse le foin. Maman sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils redescendent vers la cour.
+narrateur|La poule picore encore.
+narrateur|La vache lèche encore la pierre.
+enfant-f|Je les ai vues.
+maman|La poule, la vache, la chèvre.
+enfant-f|Et le chevreau.
+maman|Tu lui as parlé ?
+enfant-f|Oui.
+narrateur|Sarah se retourne une fois.
+narrateur|Le tas de paille cache encore les oreilles.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Elle mâche, maman. Tout près de toi. La chèvre mâche encore, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elle mâche, maman. Tout près de toi. La chèvre mâche encore, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1931,14 +2021,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2100,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Elle mâche, maman.
+maman|Tout près de toi.
+narrateur|La chèvre mâche encore, tout près.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>ferme, cour, tas de paille, rosée</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
